--- a/static/excel/MSFT_model.xlsx
+++ b/static/excel/MSFT_model.xlsx
@@ -7344,11 +7344,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>3113180.7287</v>
+        <v>3109317.9451</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $419.09</t>
+          <t>FMP marketCap  |  price $418.57</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-20</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7828,16 +7828,16 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B46" s="55">
-        <f>B8*B29+B9*B39*(1-B43)</f>
+        <f>MAX(0.085, B8*B29+B9*B39*(1-B43))</f>
         <v/>
       </c>
       <c r="C46" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8203,10 +8203,10 @@
         <v>0.1692</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>0.1666</v>
+        <v>0.1664</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.1822</v>
+        <v>0.1825</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8553,7 +8553,7 @@
         <v>329396.2</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>384288.3</v>
+        <v>384214.7</v>
       </c>
       <c r="I15" s="77" t="n">
         <v>454319.4</v>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>371,807 — 391,058</t>
+          <t>371,736 — 390,983</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
@@ -8751,7 +8751,7 @@
         <v>172559.9</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>201316</v>
+        <v>201277.5</v>
       </c>
       <c r="I20" s="77" t="n">
         <v>238003</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>194,778 — 204,862</t>
+          <t>194,740 — 204,823</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
@@ -9466,7 +9466,7 @@
         </is>
       </c>
       <c r="B38" s="100" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38" s="98" t="n"/>
       <c r="D38" s="98" t="n"/>
@@ -9480,7 +9480,7 @@
       <c r="L38" s="98" t="n"/>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>Growth tier: HIGH (12.5% 3yr avg rev growth).  Bear 14x / Base 18x / Bull 22x.  Override manually if needed.</t>
+          <t>Growth tier: HIGH (12.5% 3yr avg rev growth).  Bear 15x / Base 19x / Bull 23x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B61" s="111" t="n">
-        <v>419.09</v>
+        <v>418.57</v>
       </c>
       <c r="C61" s="103" t="n"/>
       <c r="D61" s="103" t="n"/>
@@ -10082,7 +10082,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — MSFT  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — MSFT  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 36.3x  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [+90% vs benchmark]  [trail=0.00 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=0.30]  PEG≈292.20 (trailing_pe=36.3x / rev_cagr=12%, revenue proxy)</t>
+          <t>Current 36.3x  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [+90% vs benchmark]  [trail=0.00 | fwd_pe=24.9x→2.36 | abs=1.5 → blended 40/40/20=1.24]  PEG=110.76 (fwd_pe=24.9x / eps_growth=22%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="136" t="inlineStr">
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>0.3</v>
+        <v>1.74</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 36.3x  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [+90% vs benchmark]  [trail=0.00 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=0.30]  PEG≈292.20 (trailing_pe=36.3x / rev_cagr=12%, revenue proxy)</t>
+          <t>Current 36.3x  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [+90% vs benchmark]  [trail=0.00 | fwd_pe=24.9x→2.36 | abs=1.5 → blended 40/40/20=1.24]  PEG=110.76 (fwd_pe=24.9x / eps_growth=22%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+274% vs benchmark]  [trail=0.00 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=0.30]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
+          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+274% vs benchmark]  [trail=0.00 | fwd_pfcf=37.2x→0.00 | abs=1.5 → blended 40/40/20=0.30]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+274% vs benchmark]  [trail=0.00 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=0.30]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
+          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+274% vs benchmark]  [trail=0.00 | fwd_pfcf=37.2x→0.00 | abs=1.5 → blended 40/40/20=0.30]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/MSFT_model.xlsx
+++ b/static/excel/MSFT_model.xlsx
@@ -7344,11 +7344,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>3109317.9451</v>
+        <v>3089558.3213</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $418.57</t>
+          <t>FMP marketCap  |  price $415.91</t>
         </is>
       </c>
     </row>
@@ -7659,25 +7659,27 @@
       </c>
       <c r="B32" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B33" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A1CAAAEY — AAA</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7769,7 @@
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9984,7 @@
         </is>
       </c>
       <c r="B61" s="111" t="n">
-        <v>418.57</v>
+        <v>415.91</v>
       </c>
       <c r="C61" s="103" t="n"/>
       <c r="D61" s="103" t="n"/>
@@ -10082,7 +10084,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — MSFT  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — MSFT  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10599,16 +10601,16 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 36.3x  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [+90% vs benchmark]  [trail=0.00 | fwd_pe=24.9x→2.36 | abs=1.5 → blended 40/40/20=1.24]  PEG=110.76 (fwd_pe=24.9x / eps_growth=22%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
-      <c r="E22" s="136" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>Fwd P/E 24.8x (scoring basis)  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | fwd_pe=24.8x→10.00 | abs=7.0 → blended 40/40/20=9.40]  PEG=110.32 (fwd_pe=24.8x / eps_growth=22%)  [revision:Strong upgrade cycle→+0.50]</t>
+        </is>
+      </c>
+      <c r="E22" s="135" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>1.74</v>
+        <v>9.9</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10616,7 +10618,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 36.3x  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [+90% vs benchmark]  [trail=0.00 | fwd_pe=24.9x→2.36 | abs=1.5 → blended 40/40/20=1.24]  PEG=110.76 (fwd_pe=24.9x / eps_growth=22%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 24.8x (scoring basis)  |  5yr avg 33.9x  |  Sector median 19.1x  |  DCF-implied 29.0x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | fwd_pe=24.8x→10.00 | abs=7.0 → blended 40/40/20=9.40]  PEG=110.32 (fwd_pe=24.8x / eps_growth=22%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10638,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+274% vs benchmark]  [trail=0.00 | fwd_pfcf=37.2x→0.00 | abs=1.5 → blended 40/40/20=0.30]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
+          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+25% vs benchmark]  [trail=2.97 | fwd_pfcf=36.9x→8.57 | abs=1.5 → blended 40/40/20=4.91]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10645,7 +10647,7 @@
         </is>
       </c>
       <c r="F23" s="131" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="G23" s="132">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10653,7 +10655,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+274% vs benchmark]  [trail=0.00 | fwd_pfcf=37.2x→0.00 | abs=1.5 → blended 40/40/20=0.30]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
+          <t>Current 51.6x  |  5yr avg 41.2x  |  Sector median 13.8x  |  DCF-implied 41.3x [ref only — not used as benchmark]  [+25% vs benchmark]  [trail=2.97 | fwd_pfcf=36.9x→8.57 | abs=1.5 → blended 40/40/20=4.91]  [fcf_yield=1.9% vs rf=4.6%  spread=-2.6%→modifier=-0.50]</t>
         </is>
       </c>
     </row>
